--- a/output/yearly_population_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_36_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6086</v>
+        <v>5563</v>
       </c>
       <c r="C2" t="n">
-        <v>10207</v>
+        <v>6244</v>
       </c>
       <c r="D2" t="n">
-        <v>27109</v>
+        <v>23348</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2765</v>
+        <v>3698</v>
       </c>
       <c r="C3" t="n">
-        <v>8181</v>
+        <v>3704</v>
       </c>
       <c r="D3" t="n">
-        <v>14141</v>
+        <v>16544</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2467</v>
+        <v>2815</v>
       </c>
       <c r="C4" t="n">
-        <v>4304</v>
+        <v>4328</v>
       </c>
       <c r="D4" t="n">
-        <v>6781</v>
+        <v>8244</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1620</v>
+        <v>1865</v>
       </c>
       <c r="C5" t="n">
-        <v>3648</v>
+        <v>3834</v>
       </c>
       <c r="D5" t="n">
-        <v>2734</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>1054</v>
       </c>
       <c r="C6" t="n">
-        <v>2932</v>
+        <v>2470</v>
       </c>
       <c r="D6" t="n">
-        <v>1192</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>489</v>
       </c>
       <c r="C7" t="n">
-        <v>1737</v>
+        <v>1229</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C8" t="n">
-        <v>798</v>
+        <v>536</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>246</v>
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5984</v>
+        <v>7719</v>
       </c>
       <c r="C2" t="n">
-        <v>11087</v>
+        <v>5067</v>
       </c>
       <c r="D2" t="n">
-        <v>27828</v>
+        <v>21116</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3459</v>
+        <v>3709</v>
       </c>
       <c r="C3" t="n">
-        <v>8012</v>
+        <v>4304</v>
       </c>
       <c r="D3" t="n">
-        <v>14954</v>
+        <v>16544</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2229</v>
+        <v>2745</v>
       </c>
       <c r="C4" t="n">
-        <v>6112</v>
+        <v>3926</v>
       </c>
       <c r="D4" t="n">
-        <v>7710</v>
+        <v>9268</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1759</v>
+        <v>2041</v>
       </c>
       <c r="C5" t="n">
-        <v>3845</v>
+        <v>3991</v>
       </c>
       <c r="D5" t="n">
-        <v>3311</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1108</v>
+        <v>1283</v>
       </c>
       <c r="C6" t="n">
-        <v>3232</v>
+        <v>3049</v>
       </c>
       <c r="D6" t="n">
-        <v>1401</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>559</v>
+        <v>659</v>
       </c>
       <c r="C7" t="n">
-        <v>2257</v>
+        <v>1800</v>
       </c>
       <c r="D7" t="n">
-        <v>731</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="C8" t="n">
-        <v>1211</v>
+        <v>836</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>249</v>
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6491</v>
+        <v>8831</v>
       </c>
       <c r="C2" t="n">
-        <v>16648</v>
+        <v>15774</v>
       </c>
       <c r="D2" t="n">
-        <v>26108</v>
+        <v>22963</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3664</v>
+        <v>4366</v>
       </c>
       <c r="C3" t="n">
-        <v>8322</v>
+        <v>4094</v>
       </c>
       <c r="D3" t="n">
-        <v>15620</v>
+        <v>16043</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2345</v>
+        <v>2714</v>
       </c>
       <c r="C4" t="n">
-        <v>6765</v>
+        <v>4018</v>
       </c>
       <c r="D4" t="n">
-        <v>8588</v>
+        <v>10014</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1742</v>
+        <v>2076</v>
       </c>
       <c r="C5" t="n">
-        <v>4707</v>
+        <v>3840</v>
       </c>
       <c r="D5" t="n">
-        <v>3812</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1250</v>
+        <v>1456</v>
       </c>
       <c r="C6" t="n">
-        <v>3461</v>
+        <v>3427</v>
       </c>
       <c r="D6" t="n">
-        <v>1657</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>699</v>
+        <v>822</v>
       </c>
       <c r="C7" t="n">
-        <v>2635</v>
+        <v>2307</v>
       </c>
       <c r="D7" t="n">
-        <v>808</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>324</v>
+        <v>385</v>
       </c>
       <c r="C8" t="n">
-        <v>1618</v>
+        <v>1232</v>
       </c>
       <c r="D8" t="n">
         <v>495</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C9" t="n">
-        <v>801</v>
+        <v>560</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>369</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5981</v>
+        <v>7968</v>
       </c>
       <c r="C2" t="n">
-        <v>11187</v>
+        <v>10473</v>
       </c>
       <c r="D2" t="n">
-        <v>21486</v>
+        <v>18802</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4339</v>
+        <v>5139</v>
       </c>
       <c r="C3" t="n">
-        <v>12847</v>
+        <v>7618</v>
       </c>
       <c r="D3" t="n">
-        <v>16951</v>
+        <v>17949</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1609</v>
+        <v>1918</v>
       </c>
       <c r="C4" t="n">
-        <v>8285</v>
+        <v>6000</v>
       </c>
       <c r="D4" t="n">
-        <v>8286</v>
+        <v>9769</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1155</v>
+        <v>1345</v>
       </c>
       <c r="C5" t="n">
-        <v>3391</v>
+        <v>3358</v>
       </c>
       <c r="D5" t="n">
-        <v>2685</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>645</v>
+        <v>759</v>
       </c>
       <c r="C6" t="n">
-        <v>2582</v>
+        <v>2260</v>
       </c>
       <c r="D6" t="n">
-        <v>791</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>1585</v>
+        <v>1207</v>
       </c>
       <c r="D7" t="n">
         <v>485</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>784</v>
+        <v>548</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>39</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3589</v>
+        <v>4699</v>
       </c>
       <c r="C2" t="n">
-        <v>5193</v>
+        <v>4871</v>
       </c>
       <c r="D2" t="n">
-        <v>15783</v>
+        <v>13117</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4364</v>
+        <v>5479</v>
       </c>
       <c r="C3" t="n">
-        <v>10943</v>
+        <v>8097</v>
       </c>
       <c r="D3" t="n">
-        <v>16591</v>
+        <v>17181</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2322</v>
+        <v>2785</v>
       </c>
       <c r="C4" t="n">
-        <v>10576</v>
+        <v>6882</v>
       </c>
       <c r="D4" t="n">
-        <v>9524</v>
+        <v>10822</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1260</v>
+        <v>1481</v>
       </c>
       <c r="C5" t="n">
-        <v>5503</v>
+        <v>4533</v>
       </c>
       <c r="D5" t="n">
-        <v>3353</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>775</v>
+        <v>920</v>
       </c>
       <c r="C6" t="n">
-        <v>2993</v>
+        <v>2797</v>
       </c>
       <c r="D6" t="n">
-        <v>986</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>1997</v>
+        <v>1612</v>
       </c>
       <c r="D7" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>1026</v>
+        <v>739</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
         <v>259</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>38</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3611</v>
+        <v>5369</v>
       </c>
       <c r="C2" t="n">
-        <v>7409</v>
+        <v>5560</v>
       </c>
       <c r="D2" t="n">
-        <v>13960</v>
+        <v>18855</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3391</v>
+        <v>4314</v>
       </c>
       <c r="C3" t="n">
-        <v>7307</v>
+        <v>5757</v>
       </c>
       <c r="D3" t="n">
-        <v>15492</v>
+        <v>15413</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2768</v>
+        <v>3430</v>
       </c>
       <c r="C4" t="n">
-        <v>10535</v>
+        <v>7357</v>
       </c>
       <c r="D4" t="n">
-        <v>10387</v>
+        <v>11591</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1516</v>
+        <v>1811</v>
       </c>
       <c r="C5" t="n">
-        <v>7774</v>
+        <v>5632</v>
       </c>
       <c r="D5" t="n">
-        <v>4198</v>
+        <v>4978</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>1067</v>
       </c>
       <c r="C6" t="n">
-        <v>4125</v>
+        <v>3568</v>
       </c>
       <c r="D6" t="n">
-        <v>1313</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>505</v>
       </c>
       <c r="C7" t="n">
-        <v>2445</v>
+        <v>2161</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>1425</v>
+        <v>1113</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>647</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
         <v>266</v>
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="D10" t="n">
         <v>216</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2140</v>
+        <v>3146</v>
       </c>
       <c r="C2" t="n">
-        <v>3451</v>
+        <v>2503</v>
       </c>
       <c r="D2" t="n">
-        <v>9740</v>
+        <v>12993</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3322</v>
+        <v>4412</v>
       </c>
       <c r="C3" t="n">
-        <v>7119</v>
+        <v>5494</v>
       </c>
       <c r="D3" t="n">
-        <v>14985</v>
+        <v>15428</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3042</v>
+        <v>3791</v>
       </c>
       <c r="C4" t="n">
-        <v>10273</v>
+        <v>7357</v>
       </c>
       <c r="D4" t="n">
-        <v>11051</v>
+        <v>12161</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1585</v>
+        <v>1897</v>
       </c>
       <c r="C5" t="n">
-        <v>9557</v>
+        <v>6863</v>
       </c>
       <c r="D5" t="n">
-        <v>4430</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>754</v>
+        <v>910</v>
       </c>
       <c r="C6" t="n">
-        <v>4939</v>
+        <v>4391</v>
       </c>
       <c r="D6" t="n">
-        <v>1288</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>2592</v>
+        <v>2192</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1066</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
+        <v>257</v>
+      </c>
+      <c r="D9" t="n">
         <v>292</v>
-      </c>
-      <c r="D9" t="n">
-        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>36</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2316</v>
+        <v>3758</v>
       </c>
       <c r="C2" t="n">
-        <v>4419</v>
+        <v>9367</v>
       </c>
       <c r="D2" t="n">
-        <v>10043</v>
+        <v>12235</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2428</v>
+        <v>3312</v>
       </c>
       <c r="C3" t="n">
-        <v>4865</v>
+        <v>3625</v>
       </c>
       <c r="D3" t="n">
-        <v>13408</v>
+        <v>14060</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2788</v>
+        <v>3538</v>
       </c>
       <c r="C4" t="n">
-        <v>8674</v>
+        <v>6362</v>
       </c>
       <c r="D4" t="n">
-        <v>11319</v>
+        <v>12324</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1917</v>
+        <v>2369</v>
       </c>
       <c r="C5" t="n">
-        <v>9766</v>
+        <v>7013</v>
       </c>
       <c r="D5" t="n">
-        <v>5248</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>962</v>
+        <v>1183</v>
       </c>
       <c r="C6" t="n">
-        <v>6849</v>
+        <v>5460</v>
       </c>
       <c r="D6" t="n">
-        <v>1693</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="C7" t="n">
-        <v>3536</v>
+        <v>3139</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1650</v>
+        <v>1366</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>540</v>
+        <v>462</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1745</v>
+        <v>2724</v>
       </c>
       <c r="C2" t="n">
-        <v>2526</v>
+        <v>4547</v>
       </c>
       <c r="D2" t="n">
-        <v>7393</v>
+        <v>9453</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2096</v>
+        <v>3029</v>
       </c>
       <c r="C3" t="n">
-        <v>4264</v>
+        <v>5395</v>
       </c>
       <c r="D3" t="n">
-        <v>12403</v>
+        <v>13076</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2473</v>
+        <v>3165</v>
       </c>
       <c r="C4" t="n">
-        <v>7207</v>
+        <v>5256</v>
       </c>
       <c r="D4" t="n">
-        <v>11344</v>
+        <v>12300</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2081</v>
+        <v>2605</v>
       </c>
       <c r="C5" t="n">
-        <v>9550</v>
+        <v>6892</v>
       </c>
       <c r="D5" t="n">
-        <v>5779</v>
+        <v>6879</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1122</v>
+        <v>1400</v>
       </c>
       <c r="C6" t="n">
-        <v>8007</v>
+        <v>6181</v>
       </c>
       <c r="D6" t="n">
-        <v>2029</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>258</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>4556</v>
+        <v>3944</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2098</v>
+        <v>1794</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>615</v>
+        <v>563</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2311</v>
+        <v>5213</v>
       </c>
       <c r="C2" t="n">
-        <v>15816</v>
+        <v>5411</v>
       </c>
       <c r="D2" t="n">
-        <v>17231</v>
+        <v>10806</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1663</v>
+        <v>2453</v>
       </c>
       <c r="C3" t="n">
-        <v>3222</v>
+        <v>4521</v>
       </c>
       <c r="D3" t="n">
-        <v>11008</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2036</v>
+        <v>2707</v>
       </c>
       <c r="C4" t="n">
-        <v>5773</v>
+        <v>5156</v>
       </c>
       <c r="D4" t="n">
-        <v>11151</v>
+        <v>11919</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>2580</v>
       </c>
       <c r="C5" t="n">
-        <v>8406</v>
+        <v>6123</v>
       </c>
       <c r="D5" t="n">
-        <v>6351</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1342</v>
+        <v>1688</v>
       </c>
       <c r="C6" t="n">
-        <v>8532</v>
+        <v>6407</v>
       </c>
       <c r="D6" t="n">
-        <v>2471</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>469</v>
+        <v>606</v>
       </c>
       <c r="C7" t="n">
-        <v>5883</v>
+        <v>4797</v>
       </c>
       <c r="D7" t="n">
-        <v>892</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1100</v>
+        <v>972</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
         <v>65</v>
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4573</v>
+        <v>4779</v>
       </c>
       <c r="C2" t="n">
-        <v>6839</v>
+        <v>3226</v>
       </c>
       <c r="D2" t="n">
-        <v>7223</v>
+        <v>9323</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1671</v>
+        <v>3686</v>
       </c>
       <c r="C2" t="n">
-        <v>9110</v>
+        <v>3030</v>
       </c>
       <c r="D2" t="n">
-        <v>12819</v>
+        <v>7953</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2260</v>
+        <v>3443</v>
       </c>
       <c r="C3" t="n">
-        <v>6326</v>
+        <v>5117</v>
       </c>
       <c r="D3" t="n">
-        <v>12281</v>
+        <v>12897</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2906</v>
+        <v>3741</v>
       </c>
       <c r="C4" t="n">
-        <v>8514</v>
+        <v>7292</v>
       </c>
       <c r="D4" t="n">
-        <v>11479</v>
+        <v>12357</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1277</v>
+        <v>1655</v>
       </c>
       <c r="C5" t="n">
-        <v>12179</v>
+        <v>9016</v>
       </c>
       <c r="D5" t="n">
-        <v>5783</v>
+        <v>6894</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>433</v>
+        <v>559</v>
       </c>
       <c r="C6" t="n">
-        <v>7353</v>
+        <v>6019</v>
       </c>
       <c r="D6" t="n">
-        <v>1971</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>2881</v>
+        <v>2538</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1078</v>
+        <v>952</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6054</v>
+        <v>7067</v>
       </c>
       <c r="C2" t="n">
-        <v>2883</v>
+        <v>3385</v>
       </c>
       <c r="D2" t="n">
-        <v>21791</v>
+        <v>23620</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1944</v>
+        <v>2031</v>
       </c>
       <c r="C3" t="n">
-        <v>3501</v>
+        <v>1651</v>
       </c>
       <c r="D3" t="n">
-        <v>1852</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3983</v>
+        <v>5299</v>
       </c>
       <c r="C2" t="n">
-        <v>8616</v>
+        <v>4723</v>
       </c>
       <c r="D2" t="n">
-        <v>22246</v>
+        <v>28842</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3281</v>
+        <v>3731</v>
       </c>
       <c r="C3" t="n">
-        <v>2717</v>
+        <v>2297</v>
       </c>
       <c r="D3" t="n">
-        <v>5065</v>
+        <v>5697</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>878</v>
+        <v>916</v>
       </c>
       <c r="C4" t="n">
-        <v>2093</v>
+        <v>1010</v>
       </c>
       <c r="D4" t="n">
-        <v>1554</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="5">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4232</v>
+        <v>5321</v>
       </c>
       <c r="C2" t="n">
-        <v>7561</v>
+        <v>7706</v>
       </c>
       <c r="D2" t="n">
-        <v>20013</v>
+        <v>25713</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2986</v>
+        <v>3698</v>
       </c>
       <c r="C3" t="n">
-        <v>5136</v>
+        <v>3133</v>
       </c>
       <c r="D3" t="n">
-        <v>7449</v>
+        <v>8990</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1758</v>
+        <v>1963</v>
       </c>
       <c r="C4" t="n">
-        <v>2402</v>
+        <v>1717</v>
       </c>
       <c r="D4" t="n">
-        <v>2180</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="C5" t="n">
-        <v>1238</v>
+        <v>645</v>
       </c>
       <c r="D5" t="n">
-        <v>1205</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="6">
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>175</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5111</v>
+        <v>5735</v>
       </c>
       <c r="C2" t="n">
-        <v>4608</v>
+        <v>7053</v>
       </c>
       <c r="D2" t="n">
-        <v>20213</v>
+        <v>20947</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2939</v>
+        <v>3670</v>
       </c>
       <c r="C3" t="n">
-        <v>5556</v>
+        <v>4807</v>
       </c>
       <c r="D3" t="n">
-        <v>8834</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2019</v>
+        <v>2383</v>
       </c>
       <c r="C4" t="n">
-        <v>3798</v>
+        <v>2456</v>
       </c>
       <c r="D4" t="n">
-        <v>3053</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>891</v>
+        <v>994</v>
       </c>
       <c r="C5" t="n">
-        <v>1826</v>
+        <v>1197</v>
       </c>
       <c r="D5" t="n">
-        <v>1346</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>775</v>
+        <v>470</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
         <v>659</v>
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>80</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5937</v>
+        <v>6101</v>
       </c>
       <c r="C2" t="n">
-        <v>4967</v>
+        <v>6186</v>
       </c>
       <c r="D2" t="n">
-        <v>25409</v>
+        <v>31877</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2918</v>
+        <v>3416</v>
       </c>
       <c r="C3" t="n">
-        <v>4143</v>
+        <v>4892</v>
       </c>
       <c r="D3" t="n">
-        <v>9353</v>
+        <v>10969</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1549</v>
+        <v>1891</v>
       </c>
       <c r="C4" t="n">
-        <v>3923</v>
+        <v>3096</v>
       </c>
       <c r="D4" t="n">
-        <v>3477</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>757</v>
+        <v>876</v>
       </c>
       <c r="C5" t="n">
-        <v>2098</v>
+        <v>1354</v>
       </c>
       <c r="D5" t="n">
-        <v>1310</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>874</v>
+        <v>568</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>359</v>
+        <v>264</v>
       </c>
       <c r="D7" t="n">
         <v>520</v>
@@ -5846,7 +5846,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4540</v>
+        <v>5540</v>
       </c>
       <c r="C2" t="n">
-        <v>7025</v>
+        <v>5251</v>
       </c>
       <c r="D2" t="n">
-        <v>22335</v>
+        <v>32262</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3685</v>
+        <v>4003</v>
       </c>
       <c r="C3" t="n">
-        <v>3974</v>
+        <v>4857</v>
       </c>
       <c r="D3" t="n">
-        <v>11475</v>
+        <v>13823</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1951</v>
+        <v>2315</v>
       </c>
       <c r="C4" t="n">
-        <v>3976</v>
+        <v>4135</v>
       </c>
       <c r="D4" t="n">
-        <v>4612</v>
+        <v>5423</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1036</v>
+        <v>1242</v>
       </c>
       <c r="C5" t="n">
-        <v>3140</v>
+        <v>2362</v>
       </c>
       <c r="D5" t="n">
-        <v>1707</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>480</v>
+        <v>544</v>
       </c>
       <c r="C6" t="n">
-        <v>1568</v>
+        <v>1008</v>
       </c>
       <c r="D6" t="n">
-        <v>852</v>
+        <v>876</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>651</v>
+        <v>439</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6199,7 +6199,7 @@
         <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3284</v>
+        <v>5147</v>
       </c>
       <c r="C2" t="n">
-        <v>13785</v>
+        <v>4135</v>
       </c>
       <c r="D2" t="n">
-        <v>29675</v>
+        <v>28133</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3385</v>
+        <v>3921</v>
       </c>
       <c r="C3" t="n">
-        <v>4898</v>
+        <v>4385</v>
       </c>
       <c r="D3" t="n">
-        <v>12386</v>
+        <v>15777</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2434</v>
+        <v>2730</v>
       </c>
       <c r="C4" t="n">
-        <v>3892</v>
+        <v>4464</v>
       </c>
       <c r="D4" t="n">
-        <v>5745</v>
+        <v>6818</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1305</v>
+        <v>1554</v>
       </c>
       <c r="C5" t="n">
-        <v>3540</v>
+        <v>3300</v>
       </c>
       <c r="D5" t="n">
-        <v>2212</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>693</v>
+        <v>815</v>
       </c>
       <c r="C6" t="n">
-        <v>2379</v>
+        <v>1714</v>
       </c>
       <c r="D6" t="n">
-        <v>996</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1145</v>
+        <v>745</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>479</v>
+        <v>345</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>

--- a/output/yearly_population_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_36_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5563</v>
+        <v>6075</v>
       </c>
       <c r="C2" t="n">
-        <v>6244</v>
+        <v>6764</v>
       </c>
       <c r="D2" t="n">
-        <v>23348</v>
+        <v>16778</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3698</v>
+        <v>3539</v>
       </c>
       <c r="C3" t="n">
-        <v>3704</v>
+        <v>6403</v>
       </c>
       <c r="D3" t="n">
-        <v>16544</v>
+        <v>10616</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2815</v>
+        <v>2691</v>
       </c>
       <c r="C4" t="n">
-        <v>4328</v>
+        <v>5103</v>
       </c>
       <c r="D4" t="n">
-        <v>8244</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1865</v>
+        <v>1665</v>
       </c>
       <c r="C5" t="n">
-        <v>3834</v>
+        <v>4981</v>
       </c>
       <c r="D5" t="n">
-        <v>3162</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1054</v>
+        <v>921</v>
       </c>
       <c r="C6" t="n">
-        <v>2470</v>
+        <v>3459</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>432</v>
       </c>
       <c r="C7" t="n">
-        <v>1229</v>
+        <v>2096</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>536</v>
+        <v>1133</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>479</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7719</v>
+        <v>7163</v>
       </c>
       <c r="C2" t="n">
-        <v>5067</v>
+        <v>12257</v>
       </c>
       <c r="D2" t="n">
-        <v>21116</v>
+        <v>15588</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3709</v>
+        <v>3820</v>
       </c>
       <c r="C3" t="n">
-        <v>4304</v>
+        <v>5779</v>
       </c>
       <c r="D3" t="n">
-        <v>16544</v>
+        <v>10740</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2745</v>
+        <v>2611</v>
       </c>
       <c r="C4" t="n">
-        <v>3926</v>
+        <v>5620</v>
       </c>
       <c r="D4" t="n">
-        <v>9268</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2041</v>
+        <v>1855</v>
       </c>
       <c r="C5" t="n">
-        <v>3991</v>
+        <v>4885</v>
       </c>
       <c r="D5" t="n">
-        <v>3895</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1283</v>
+        <v>1127</v>
       </c>
       <c r="C6" t="n">
-        <v>3049</v>
+        <v>4111</v>
       </c>
       <c r="D6" t="n">
-        <v>1547</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>659</v>
+        <v>578</v>
       </c>
       <c r="C7" t="n">
-        <v>1800</v>
+        <v>2675</v>
       </c>
       <c r="D7" t="n">
-        <v>758</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="C8" t="n">
-        <v>836</v>
+        <v>1547</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>743</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8831</v>
+        <v>8429</v>
       </c>
       <c r="C2" t="n">
-        <v>15774</v>
+        <v>13698</v>
       </c>
       <c r="D2" t="n">
-        <v>22963</v>
+        <v>29381</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4366</v>
+        <v>4195</v>
       </c>
       <c r="C3" t="n">
-        <v>4094</v>
+        <v>7561</v>
       </c>
       <c r="D3" t="n">
-        <v>16043</v>
+        <v>10759</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2714</v>
+        <v>2638</v>
       </c>
       <c r="C4" t="n">
-        <v>4018</v>
+        <v>5517</v>
       </c>
       <c r="D4" t="n">
-        <v>10014</v>
+        <v>6578</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2076</v>
+        <v>1937</v>
       </c>
       <c r="C5" t="n">
-        <v>3840</v>
+        <v>5046</v>
       </c>
       <c r="D5" t="n">
-        <v>4601</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1456</v>
+        <v>1287</v>
       </c>
       <c r="C6" t="n">
-        <v>3427</v>
+        <v>4393</v>
       </c>
       <c r="D6" t="n">
-        <v>1849</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>822</v>
+        <v>711</v>
       </c>
       <c r="C7" t="n">
-        <v>2307</v>
+        <v>3224</v>
       </c>
       <c r="D7" t="n">
-        <v>866</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>385</v>
+        <v>329</v>
       </c>
       <c r="C8" t="n">
-        <v>1232</v>
+        <v>1973</v>
       </c>
       <c r="D8" t="n">
-        <v>495</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C9" t="n">
-        <v>560</v>
+        <v>1049</v>
       </c>
       <c r="D9" t="n">
-        <v>340</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>477</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7968</v>
+        <v>7680</v>
       </c>
       <c r="C2" t="n">
-        <v>10473</v>
+        <v>9314</v>
       </c>
       <c r="D2" t="n">
-        <v>18802</v>
+        <v>24021</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5139</v>
+        <v>4892</v>
       </c>
       <c r="C3" t="n">
-        <v>7618</v>
+        <v>11179</v>
       </c>
       <c r="D3" t="n">
-        <v>17949</v>
+        <v>11832</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1918</v>
+        <v>1789</v>
       </c>
       <c r="C4" t="n">
-        <v>6000</v>
+        <v>7863</v>
       </c>
       <c r="D4" t="n">
-        <v>9769</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1345</v>
+        <v>1189</v>
       </c>
       <c r="C5" t="n">
-        <v>3358</v>
+        <v>4305</v>
       </c>
       <c r="D5" t="n">
-        <v>3092</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>759</v>
+        <v>656</v>
       </c>
       <c r="C6" t="n">
-        <v>2260</v>
+        <v>3159</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>1207</v>
+        <v>1933</v>
       </c>
       <c r="D7" t="n">
-        <v>485</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>548</v>
+        <v>1028</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>467</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4699</v>
+        <v>4609</v>
       </c>
       <c r="C2" t="n">
-        <v>4871</v>
+        <v>4436</v>
       </c>
       <c r="D2" t="n">
-        <v>13117</v>
+        <v>16998</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5479</v>
+        <v>5208</v>
       </c>
       <c r="C3" t="n">
-        <v>8097</v>
+        <v>9380</v>
       </c>
       <c r="D3" t="n">
-        <v>17181</v>
+        <v>12808</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2785</v>
+        <v>2560</v>
       </c>
       <c r="C4" t="n">
-        <v>6882</v>
+        <v>9453</v>
       </c>
       <c r="D4" t="n">
-        <v>10822</v>
+        <v>7187</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1481</v>
+        <v>1336</v>
       </c>
       <c r="C5" t="n">
-        <v>4533</v>
+        <v>5890</v>
       </c>
       <c r="D5" t="n">
-        <v>3984</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>920</v>
+        <v>779</v>
       </c>
       <c r="C6" t="n">
-        <v>2797</v>
+        <v>3747</v>
       </c>
       <c r="D6" t="n">
-        <v>1078</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>1612</v>
+        <v>2408</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>739</v>
+        <v>1335</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>514</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5369</v>
+        <v>4129</v>
       </c>
       <c r="C2" t="n">
-        <v>5560</v>
+        <v>7160</v>
       </c>
       <c r="D2" t="n">
-        <v>18855</v>
+        <v>22493</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4314</v>
+        <v>4166</v>
       </c>
       <c r="C3" t="n">
-        <v>5757</v>
+        <v>6257</v>
       </c>
       <c r="D3" t="n">
-        <v>15413</v>
+        <v>12517</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3430</v>
+        <v>3149</v>
       </c>
       <c r="C4" t="n">
-        <v>7357</v>
+        <v>9220</v>
       </c>
       <c r="D4" t="n">
-        <v>11591</v>
+        <v>7885</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1811</v>
+        <v>1640</v>
       </c>
       <c r="C5" t="n">
-        <v>5632</v>
+        <v>7500</v>
       </c>
       <c r="D5" t="n">
-        <v>4978</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1067</v>
+        <v>933</v>
       </c>
       <c r="C6" t="n">
-        <v>3568</v>
+        <v>4657</v>
       </c>
       <c r="D6" t="n">
-        <v>1509</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>418</v>
       </c>
       <c r="C7" t="n">
-        <v>2161</v>
+        <v>3008</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1113</v>
+        <v>1778</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>502</v>
+        <v>824</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3146</v>
+        <v>2484</v>
       </c>
       <c r="C2" t="n">
-        <v>2503</v>
+        <v>3400</v>
       </c>
       <c r="D2" t="n">
-        <v>12993</v>
+        <v>15683</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4412</v>
+        <v>4012</v>
       </c>
       <c r="C3" t="n">
-        <v>5494</v>
+        <v>6370</v>
       </c>
       <c r="D3" t="n">
-        <v>15428</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3791</v>
+        <v>3462</v>
       </c>
       <c r="C4" t="n">
-        <v>7357</v>
+        <v>9034</v>
       </c>
       <c r="D4" t="n">
-        <v>12161</v>
+        <v>8456</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1897</v>
+        <v>1679</v>
       </c>
       <c r="C5" t="n">
-        <v>6863</v>
+        <v>8972</v>
       </c>
       <c r="D5" t="n">
-        <v>5371</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>910</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>4391</v>
+        <v>5622</v>
       </c>
       <c r="D6" t="n">
-        <v>1473</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2192</v>
+        <v>3177</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>851</v>
+        <v>1347</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3758</v>
+        <v>3319</v>
       </c>
       <c r="C2" t="n">
-        <v>9367</v>
+        <v>12422</v>
       </c>
       <c r="D2" t="n">
-        <v>12235</v>
+        <v>15098</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3312</v>
+        <v>2899</v>
       </c>
       <c r="C3" t="n">
-        <v>3625</v>
+        <v>4478</v>
       </c>
       <c r="D3" t="n">
-        <v>14060</v>
+        <v>12837</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3538</v>
+        <v>3250</v>
       </c>
       <c r="C4" t="n">
-        <v>6362</v>
+        <v>7679</v>
       </c>
       <c r="D4" t="n">
-        <v>12324</v>
+        <v>8938</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2369</v>
+        <v>2102</v>
       </c>
       <c r="C5" t="n">
-        <v>7013</v>
+        <v>8898</v>
       </c>
       <c r="D5" t="n">
-        <v>6250</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1183</v>
+        <v>996</v>
       </c>
       <c r="C6" t="n">
-        <v>5460</v>
+        <v>7009</v>
       </c>
       <c r="D6" t="n">
-        <v>2029</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>3139</v>
+        <v>4165</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1366</v>
+        <v>2049</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>462</v>
+        <v>658</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2724</v>
+        <v>2241</v>
       </c>
       <c r="C2" t="n">
-        <v>4547</v>
+        <v>5988</v>
       </c>
       <c r="D2" t="n">
-        <v>9453</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3029</v>
+        <v>2658</v>
       </c>
       <c r="C3" t="n">
-        <v>5395</v>
+        <v>6865</v>
       </c>
       <c r="D3" t="n">
-        <v>13076</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3165</v>
+        <v>2900</v>
       </c>
       <c r="C4" t="n">
-        <v>5256</v>
+        <v>6449</v>
       </c>
       <c r="D4" t="n">
-        <v>12300</v>
+        <v>9238</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2605</v>
+        <v>2318</v>
       </c>
       <c r="C5" t="n">
-        <v>6892</v>
+        <v>8621</v>
       </c>
       <c r="D5" t="n">
-        <v>6879</v>
+        <v>4548</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1400</v>
+        <v>1174</v>
       </c>
       <c r="C6" t="n">
-        <v>6181</v>
+        <v>7868</v>
       </c>
       <c r="D6" t="n">
-        <v>2409</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>3944</v>
+        <v>5117</v>
       </c>
       <c r="D7" t="n">
-        <v>809</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1794</v>
+        <v>2572</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>563</v>
+        <v>744</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5213</v>
+        <v>3641</v>
       </c>
       <c r="C2" t="n">
-        <v>5411</v>
+        <v>14395</v>
       </c>
       <c r="D2" t="n">
-        <v>10806</v>
+        <v>16883</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2453</v>
+        <v>2117</v>
       </c>
       <c r="C3" t="n">
-        <v>4521</v>
+        <v>5864</v>
       </c>
       <c r="D3" t="n">
-        <v>11880</v>
+        <v>11548</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2707</v>
+        <v>2448</v>
       </c>
       <c r="C4" t="n">
-        <v>5156</v>
+        <v>6486</v>
       </c>
       <c r="D4" t="n">
-        <v>11919</v>
+        <v>9431</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2580</v>
+        <v>2314</v>
       </c>
       <c r="C5" t="n">
-        <v>6123</v>
+        <v>7586</v>
       </c>
       <c r="D5" t="n">
-        <v>7450</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1688</v>
+        <v>1423</v>
       </c>
       <c r="C6" t="n">
-        <v>6407</v>
+        <v>8085</v>
       </c>
       <c r="D6" t="n">
-        <v>2978</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>606</v>
+        <v>485</v>
       </c>
       <c r="C7" t="n">
-        <v>4797</v>
+        <v>6112</v>
       </c>
       <c r="D7" t="n">
-        <v>1004</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>2590</v>
+        <v>3443</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>972</v>
+        <v>1342</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>5330</v>
       </c>
       <c r="C2" t="n">
-        <v>3226</v>
+        <v>12101</v>
       </c>
       <c r="D2" t="n">
-        <v>9323</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3686</v>
+        <v>2632</v>
       </c>
       <c r="C2" t="n">
-        <v>3030</v>
+        <v>8406</v>
       </c>
       <c r="D2" t="n">
-        <v>7953</v>
+        <v>12560</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3443</v>
+        <v>2908</v>
       </c>
       <c r="C3" t="n">
-        <v>5117</v>
+        <v>8232</v>
       </c>
       <c r="D3" t="n">
-        <v>12897</v>
+        <v>12665</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3741</v>
+        <v>3367</v>
       </c>
       <c r="C4" t="n">
-        <v>7292</v>
+        <v>9209</v>
       </c>
       <c r="D4" t="n">
-        <v>12357</v>
+        <v>9629</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1655</v>
+        <v>1357</v>
       </c>
       <c r="C5" t="n">
-        <v>9016</v>
+        <v>11224</v>
       </c>
       <c r="D5" t="n">
-        <v>6894</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>559</v>
+        <v>448</v>
       </c>
       <c r="C6" t="n">
-        <v>6019</v>
+        <v>7495</v>
       </c>
       <c r="D6" t="n">
-        <v>2315</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>2538</v>
+        <v>3374</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>952</v>
+        <v>1315</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7067</v>
+        <v>5849</v>
       </c>
       <c r="C2" t="n">
-        <v>3385</v>
+        <v>5934</v>
       </c>
       <c r="D2" t="n">
-        <v>23620</v>
+        <v>17530</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2031</v>
+        <v>2265</v>
       </c>
       <c r="C3" t="n">
-        <v>1651</v>
+        <v>6098</v>
       </c>
       <c r="D3" t="n">
-        <v>2280</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5299</v>
+        <v>4064</v>
       </c>
       <c r="C2" t="n">
-        <v>4723</v>
+        <v>3317</v>
       </c>
       <c r="D2" t="n">
-        <v>28842</v>
+        <v>16944</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3731</v>
+        <v>3331</v>
       </c>
       <c r="C3" t="n">
-        <v>2297</v>
+        <v>5178</v>
       </c>
       <c r="D3" t="n">
-        <v>5697</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>916</v>
+        <v>1018</v>
       </c>
       <c r="C4" t="n">
-        <v>1010</v>
+        <v>3617</v>
       </c>
       <c r="D4" t="n">
-        <v>1640</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5321</v>
+        <v>4626</v>
       </c>
       <c r="C2" t="n">
-        <v>7706</v>
+        <v>8685</v>
       </c>
       <c r="D2" t="n">
-        <v>25713</v>
+        <v>15243</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3698</v>
+        <v>3040</v>
       </c>
       <c r="C3" t="n">
-        <v>3133</v>
+        <v>3603</v>
       </c>
       <c r="D3" t="n">
-        <v>8990</v>
+        <v>5953</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1963</v>
+        <v>1850</v>
       </c>
       <c r="C4" t="n">
-        <v>1717</v>
+        <v>4425</v>
       </c>
       <c r="D4" t="n">
-        <v>2369</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="C5" t="n">
-        <v>645</v>
+        <v>2073</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5735</v>
+        <v>5690</v>
       </c>
       <c r="C2" t="n">
-        <v>7053</v>
+        <v>10191</v>
       </c>
       <c r="D2" t="n">
-        <v>20947</v>
+        <v>18279</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3670</v>
+        <v>3112</v>
       </c>
       <c r="C3" t="n">
-        <v>4807</v>
+        <v>5412</v>
       </c>
       <c r="D3" t="n">
-        <v>10899</v>
+        <v>6945</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2383</v>
+        <v>2084</v>
       </c>
       <c r="C4" t="n">
-        <v>2456</v>
+        <v>3891</v>
       </c>
       <c r="D4" t="n">
-        <v>3481</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>994</v>
+        <v>952</v>
       </c>
       <c r="C5" t="n">
-        <v>1197</v>
+        <v>3229</v>
       </c>
       <c r="D5" t="n">
-        <v>1393</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>470</v>
+        <v>1200</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6101</v>
+        <v>5662</v>
       </c>
       <c r="C2" t="n">
-        <v>6186</v>
+        <v>7985</v>
       </c>
       <c r="D2" t="n">
-        <v>31877</v>
+        <v>21195</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3416</v>
+        <v>3165</v>
       </c>
       <c r="C3" t="n">
-        <v>4892</v>
+        <v>6434</v>
       </c>
       <c r="D3" t="n">
-        <v>10969</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1891</v>
+        <v>1602</v>
       </c>
       <c r="C4" t="n">
-        <v>3096</v>
+        <v>3874</v>
       </c>
       <c r="D4" t="n">
-        <v>4097</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>876</v>
+        <v>797</v>
       </c>
       <c r="C5" t="n">
-        <v>1354</v>
+        <v>2581</v>
       </c>
       <c r="D5" t="n">
-        <v>1404</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>568</v>
+        <v>1497</v>
       </c>
       <c r="D6" t="n">
-        <v>774</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>264</v>
+        <v>490</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5540</v>
+        <v>5978</v>
       </c>
       <c r="C2" t="n">
-        <v>5251</v>
+        <v>4944</v>
       </c>
       <c r="D2" t="n">
-        <v>32262</v>
+        <v>19032</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4003</v>
+        <v>3668</v>
       </c>
       <c r="C3" t="n">
-        <v>4857</v>
+        <v>6309</v>
       </c>
       <c r="D3" t="n">
-        <v>13823</v>
+        <v>9395</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2315</v>
+        <v>2097</v>
       </c>
       <c r="C4" t="n">
-        <v>4135</v>
+        <v>5341</v>
       </c>
       <c r="D4" t="n">
-        <v>5423</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1242</v>
+        <v>1071</v>
       </c>
       <c r="C5" t="n">
-        <v>2362</v>
+        <v>3284</v>
       </c>
       <c r="D5" t="n">
-        <v>1904</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>544</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>1008</v>
+        <v>2078</v>
       </c>
       <c r="D6" t="n">
-        <v>876</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>439</v>
+        <v>1062</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>245</v>
+        <v>368</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>198</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5147</v>
+        <v>4707</v>
       </c>
       <c r="C2" t="n">
-        <v>4135</v>
+        <v>9900</v>
       </c>
       <c r="D2" t="n">
-        <v>28133</v>
+        <v>17637</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3921</v>
+        <v>3937</v>
       </c>
       <c r="C3" t="n">
-        <v>4385</v>
+        <v>4816</v>
       </c>
       <c r="D3" t="n">
-        <v>15777</v>
+        <v>10260</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2730</v>
+        <v>2478</v>
       </c>
       <c r="C4" t="n">
-        <v>4464</v>
+        <v>5778</v>
       </c>
       <c r="D4" t="n">
-        <v>6818</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1554</v>
+        <v>1374</v>
       </c>
       <c r="C5" t="n">
-        <v>3300</v>
+        <v>4341</v>
       </c>
       <c r="D5" t="n">
-        <v>2521</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>815</v>
+        <v>712</v>
       </c>
       <c r="C6" t="n">
-        <v>1714</v>
+        <v>2670</v>
       </c>
       <c r="D6" t="n">
-        <v>1051</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="C7" t="n">
-        <v>745</v>
+        <v>1599</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>345</v>
+        <v>721</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6524,7 +6524,7 @@
         <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_36_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6075</v>
+        <v>901</v>
       </c>
       <c r="C2" t="n">
-        <v>6764</v>
+        <v>3855</v>
       </c>
       <c r="D2" t="n">
-        <v>16778</v>
+        <v>16515</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3539</v>
+        <v>1795</v>
       </c>
       <c r="C3" t="n">
-        <v>6403</v>
+        <v>9671</v>
       </c>
       <c r="D3" t="n">
-        <v>10616</v>
+        <v>13268</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2691</v>
+        <v>1284</v>
       </c>
       <c r="C4" t="n">
-        <v>5103</v>
+        <v>10293</v>
       </c>
       <c r="D4" t="n">
-        <v>5500</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1665</v>
+        <v>592</v>
       </c>
       <c r="C5" t="n">
-        <v>4981</v>
+        <v>5408</v>
       </c>
       <c r="D5" t="n">
-        <v>2301</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>921</v>
+        <v>234</v>
       </c>
       <c r="C6" t="n">
-        <v>3459</v>
+        <v>1926</v>
       </c>
       <c r="D6" t="n">
-        <v>1074</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>432</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>2096</v>
+        <v>623</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1133</v>
+        <v>333</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>479</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7163</v>
+        <v>714</v>
       </c>
       <c r="C2" t="n">
-        <v>12257</v>
+        <v>11856</v>
       </c>
       <c r="D2" t="n">
-        <v>15588</v>
+        <v>19497</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3820</v>
+        <v>1164</v>
       </c>
       <c r="C3" t="n">
-        <v>5779</v>
+        <v>5842</v>
       </c>
       <c r="D3" t="n">
-        <v>10740</v>
+        <v>12827</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2611</v>
+        <v>1327</v>
       </c>
       <c r="C4" t="n">
-        <v>5620</v>
+        <v>9744</v>
       </c>
       <c r="D4" t="n">
-        <v>6167</v>
+        <v>6663</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1855</v>
+        <v>798</v>
       </c>
       <c r="C5" t="n">
-        <v>4885</v>
+        <v>7879</v>
       </c>
       <c r="D5" t="n">
-        <v>2700</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1127</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>4111</v>
+        <v>3629</v>
       </c>
       <c r="D6" t="n">
-        <v>1248</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>578</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2675</v>
+        <v>1241</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1547</v>
+        <v>464</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>743</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8429</v>
+        <v>388</v>
       </c>
       <c r="C2" t="n">
-        <v>13698</v>
+        <v>5097</v>
       </c>
       <c r="D2" t="n">
-        <v>29381</v>
+        <v>13279</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4195</v>
+        <v>1001</v>
       </c>
       <c r="C3" t="n">
-        <v>7561</v>
+        <v>7822</v>
       </c>
       <c r="D3" t="n">
-        <v>10759</v>
+        <v>13299</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2638</v>
+        <v>1427</v>
       </c>
       <c r="C4" t="n">
-        <v>5517</v>
+        <v>9071</v>
       </c>
       <c r="D4" t="n">
-        <v>6578</v>
+        <v>7431</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1937</v>
+        <v>790</v>
       </c>
       <c r="C5" t="n">
-        <v>5046</v>
+        <v>9368</v>
       </c>
       <c r="D5" t="n">
-        <v>3091</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>4393</v>
+        <v>4617</v>
       </c>
       <c r="D6" t="n">
-        <v>1440</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>711</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3224</v>
+        <v>1171</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>329</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1973</v>
+        <v>463</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1049</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>477</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7680</v>
+        <v>1050</v>
       </c>
       <c r="C2" t="n">
-        <v>9314</v>
+        <v>6490</v>
       </c>
       <c r="D2" t="n">
-        <v>24021</v>
+        <v>16440</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4892</v>
+        <v>622</v>
       </c>
       <c r="C3" t="n">
-        <v>11179</v>
+        <v>5731</v>
       </c>
       <c r="D3" t="n">
-        <v>11832</v>
+        <v>12381</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1789</v>
+        <v>1108</v>
       </c>
       <c r="C4" t="n">
-        <v>7863</v>
+        <v>8246</v>
       </c>
       <c r="D4" t="n">
-        <v>6430</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1189</v>
+        <v>948</v>
       </c>
       <c r="C5" t="n">
-        <v>4305</v>
+        <v>9207</v>
       </c>
       <c r="D5" t="n">
-        <v>2242</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>656</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>3159</v>
+        <v>6760</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>1933</v>
+        <v>2679</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1028</v>
+        <v>749</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>467</v>
+        <v>327</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4609</v>
+        <v>569</v>
       </c>
       <c r="C2" t="n">
-        <v>4436</v>
+        <v>3480</v>
       </c>
       <c r="D2" t="n">
-        <v>16998</v>
+        <v>12199</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5208</v>
+        <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>9380</v>
+        <v>5515</v>
       </c>
       <c r="D3" t="n">
-        <v>12808</v>
+        <v>12207</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2560</v>
+        <v>873</v>
       </c>
       <c r="C4" t="n">
-        <v>9453</v>
+        <v>7201</v>
       </c>
       <c r="D4" t="n">
-        <v>7187</v>
+        <v>8647</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1336</v>
+        <v>981</v>
       </c>
       <c r="C5" t="n">
-        <v>5890</v>
+        <v>8990</v>
       </c>
       <c r="D5" t="n">
-        <v>2739</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>779</v>
+        <v>539</v>
       </c>
       <c r="C6" t="n">
-        <v>3747</v>
+        <v>7863</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2408</v>
+        <v>3981</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1335</v>
+        <v>1187</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>406</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4129</v>
+        <v>451</v>
       </c>
       <c r="C2" t="n">
-        <v>7160</v>
+        <v>8253</v>
       </c>
       <c r="D2" t="n">
-        <v>22493</v>
+        <v>12296</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4166</v>
+        <v>532</v>
       </c>
       <c r="C3" t="n">
-        <v>6257</v>
+        <v>4089</v>
       </c>
       <c r="D3" t="n">
-        <v>12517</v>
+        <v>11405</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3149</v>
+        <v>699</v>
       </c>
       <c r="C4" t="n">
-        <v>9220</v>
+        <v>6274</v>
       </c>
       <c r="D4" t="n">
-        <v>7885</v>
+        <v>8930</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1640</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>7500</v>
+        <v>8099</v>
       </c>
       <c r="D5" t="n">
-        <v>3338</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>933</v>
+        <v>651</v>
       </c>
       <c r="C6" t="n">
-        <v>4657</v>
+        <v>8257</v>
       </c>
       <c r="D6" t="n">
-        <v>1147</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>3008</v>
+        <v>5578</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1778</v>
+        <v>2227</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>824</v>
+        <v>685</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2484</v>
+        <v>313</v>
       </c>
       <c r="C2" t="n">
-        <v>3400</v>
+        <v>4490</v>
       </c>
       <c r="D2" t="n">
-        <v>15683</v>
+        <v>8951</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4012</v>
+        <v>708</v>
       </c>
       <c r="C3" t="n">
-        <v>6370</v>
+        <v>5488</v>
       </c>
       <c r="D3" t="n">
-        <v>13274</v>
+        <v>12348</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3462</v>
+        <v>1147</v>
       </c>
       <c r="C4" t="n">
-        <v>9034</v>
+        <v>8905</v>
       </c>
       <c r="D4" t="n">
-        <v>8456</v>
+        <v>9093</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1679</v>
+        <v>641</v>
       </c>
       <c r="C5" t="n">
-        <v>8972</v>
+        <v>11673</v>
       </c>
       <c r="D5" t="n">
-        <v>3523</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>227</v>
       </c>
       <c r="C6" t="n">
-        <v>5622</v>
+        <v>7327</v>
       </c>
       <c r="D6" t="n">
-        <v>1137</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>3177</v>
+        <v>2182</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1347</v>
+        <v>671</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3319</v>
+        <v>171</v>
       </c>
       <c r="C2" t="n">
-        <v>12422</v>
+        <v>2136</v>
       </c>
       <c r="D2" t="n">
-        <v>15098</v>
+        <v>6856</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2899</v>
+        <v>465</v>
       </c>
       <c r="C3" t="n">
-        <v>4478</v>
+        <v>4433</v>
       </c>
       <c r="D3" t="n">
-        <v>12837</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3250</v>
+        <v>791</v>
       </c>
       <c r="C4" t="n">
-        <v>7679</v>
+        <v>6842</v>
       </c>
       <c r="D4" t="n">
-        <v>8938</v>
+        <v>8952</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2102</v>
+        <v>601</v>
       </c>
       <c r="C5" t="n">
-        <v>8898</v>
+        <v>9141</v>
       </c>
       <c r="D5" t="n">
-        <v>4126</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>221</v>
       </c>
       <c r="C6" t="n">
-        <v>7009</v>
+        <v>7531</v>
       </c>
       <c r="D6" t="n">
-        <v>1442</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n">
-        <v>4165</v>
+        <v>3037</v>
       </c>
       <c r="D7" t="n">
-        <v>635</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>2049</v>
+        <v>788</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>658</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>119</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2241</v>
+        <v>482</v>
       </c>
       <c r="C2" t="n">
-        <v>5988</v>
+        <v>2593</v>
       </c>
       <c r="D2" t="n">
-        <v>11009</v>
+        <v>11528</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2658</v>
+        <v>276</v>
       </c>
       <c r="C3" t="n">
-        <v>6865</v>
+        <v>2829</v>
       </c>
       <c r="D3" t="n">
-        <v>12533</v>
+        <v>9609</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2900</v>
+        <v>566</v>
       </c>
       <c r="C4" t="n">
-        <v>6449</v>
+        <v>5470</v>
       </c>
       <c r="D4" t="n">
-        <v>9238</v>
+        <v>9056</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2318</v>
+        <v>622</v>
       </c>
       <c r="C5" t="n">
-        <v>8621</v>
+        <v>7781</v>
       </c>
       <c r="D5" t="n">
-        <v>4548</v>
+        <v>4935</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1174</v>
+        <v>350</v>
       </c>
       <c r="C6" t="n">
-        <v>7868</v>
+        <v>8239</v>
       </c>
       <c r="D6" t="n">
-        <v>1698</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>5117</v>
+        <v>5223</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2572</v>
+        <v>1809</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>744</v>
+        <v>483</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3641</v>
+        <v>770</v>
       </c>
       <c r="C2" t="n">
-        <v>14395</v>
+        <v>4657</v>
       </c>
       <c r="D2" t="n">
-        <v>16883</v>
+        <v>9537</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2117</v>
+        <v>298</v>
       </c>
       <c r="C3" t="n">
-        <v>5864</v>
+        <v>2388</v>
       </c>
       <c r="D3" t="n">
-        <v>11548</v>
+        <v>9224</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2448</v>
+        <v>388</v>
       </c>
       <c r="C4" t="n">
-        <v>6486</v>
+        <v>4063</v>
       </c>
       <c r="D4" t="n">
-        <v>9431</v>
+        <v>8784</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2314</v>
+        <v>543</v>
       </c>
       <c r="C5" t="n">
-        <v>7586</v>
+        <v>6532</v>
       </c>
       <c r="D5" t="n">
-        <v>5040</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>427</v>
       </c>
       <c r="C6" t="n">
-        <v>8085</v>
+        <v>7951</v>
       </c>
       <c r="D6" t="n">
-        <v>2031</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>485</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>6112</v>
+        <v>6499</v>
       </c>
       <c r="D7" t="n">
-        <v>808</v>
+        <v>878</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>3443</v>
+        <v>3280</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1342</v>
+        <v>1028</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>391</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5330</v>
+        <v>2365</v>
       </c>
       <c r="C2" t="n">
-        <v>12101</v>
+        <v>5547</v>
       </c>
       <c r="D2" t="n">
-        <v>6221</v>
+        <v>6603</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2632</v>
+        <v>633</v>
       </c>
       <c r="C2" t="n">
-        <v>8406</v>
+        <v>7426</v>
       </c>
       <c r="D2" t="n">
-        <v>12560</v>
+        <v>11277</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2908</v>
+        <v>391</v>
       </c>
       <c r="C3" t="n">
-        <v>8232</v>
+        <v>2951</v>
       </c>
       <c r="D3" t="n">
-        <v>12665</v>
+        <v>8658</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3367</v>
+        <v>304</v>
       </c>
       <c r="C4" t="n">
-        <v>9209</v>
+        <v>3238</v>
       </c>
       <c r="D4" t="n">
-        <v>9629</v>
+        <v>8584</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1357</v>
+        <v>448</v>
       </c>
       <c r="C5" t="n">
-        <v>11224</v>
+        <v>5290</v>
       </c>
       <c r="D5" t="n">
-        <v>4643</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C6" t="n">
-        <v>7495</v>
+        <v>7293</v>
       </c>
       <c r="D6" t="n">
-        <v>1664</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>249</v>
       </c>
       <c r="C7" t="n">
-        <v>3374</v>
+        <v>7016</v>
       </c>
       <c r="D7" t="n">
-        <v>529</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>1315</v>
+        <v>4540</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>1866</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>550</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5849</v>
+        <v>4710</v>
       </c>
       <c r="C2" t="n">
-        <v>5934</v>
+        <v>13246</v>
       </c>
       <c r="D2" t="n">
-        <v>17530</v>
+        <v>11340</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2265</v>
+        <v>784</v>
       </c>
       <c r="C3" t="n">
-        <v>6098</v>
+        <v>2190</v>
       </c>
       <c r="D3" t="n">
-        <v>1684</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4064</v>
+        <v>3292</v>
       </c>
       <c r="C2" t="n">
-        <v>3317</v>
+        <v>7146</v>
       </c>
       <c r="D2" t="n">
-        <v>16944</v>
+        <v>23871</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3331</v>
+        <v>2341</v>
       </c>
       <c r="C3" t="n">
-        <v>5178</v>
+        <v>7623</v>
       </c>
       <c r="D3" t="n">
-        <v>4222</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1018</v>
+        <v>390</v>
       </c>
       <c r="C4" t="n">
-        <v>3617</v>
+        <v>1414</v>
       </c>
       <c r="D4" t="n">
-        <v>1520</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4626</v>
+        <v>1876</v>
       </c>
       <c r="C2" t="n">
-        <v>8685</v>
+        <v>6294</v>
       </c>
       <c r="D2" t="n">
-        <v>15243</v>
+        <v>20918</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3040</v>
+        <v>2326</v>
       </c>
       <c r="C3" t="n">
-        <v>3603</v>
+        <v>6309</v>
       </c>
       <c r="D3" t="n">
-        <v>5953</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1850</v>
+        <v>1203</v>
       </c>
       <c r="C4" t="n">
-        <v>4425</v>
+        <v>5139</v>
       </c>
       <c r="D4" t="n">
-        <v>1992</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>470</v>
+        <v>212</v>
       </c>
       <c r="C5" t="n">
-        <v>2073</v>
+        <v>909</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>289</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5690</v>
+        <v>2363</v>
       </c>
       <c r="C2" t="n">
-        <v>10191</v>
+        <v>8218</v>
       </c>
       <c r="D2" t="n">
-        <v>18279</v>
+        <v>20694</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3112</v>
+        <v>1741</v>
       </c>
       <c r="C3" t="n">
-        <v>5412</v>
+        <v>5443</v>
       </c>
       <c r="D3" t="n">
-        <v>6945</v>
+        <v>8253</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2084</v>
+        <v>1523</v>
       </c>
       <c r="C4" t="n">
-        <v>3891</v>
+        <v>5706</v>
       </c>
       <c r="D4" t="n">
-        <v>2653</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>952</v>
+        <v>597</v>
       </c>
       <c r="C5" t="n">
-        <v>3229</v>
+        <v>3245</v>
       </c>
       <c r="D5" t="n">
-        <v>1295</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>270</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>1200</v>
+        <v>605</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5662</v>
+        <v>2353</v>
       </c>
       <c r="C2" t="n">
-        <v>7985</v>
+        <v>12291</v>
       </c>
       <c r="D2" t="n">
-        <v>21195</v>
+        <v>23020</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3165</v>
+        <v>1674</v>
       </c>
       <c r="C3" t="n">
-        <v>6434</v>
+        <v>5980</v>
       </c>
       <c r="D3" t="n">
-        <v>7694</v>
+        <v>9563</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1602</v>
+        <v>1410</v>
       </c>
       <c r="C4" t="n">
-        <v>3874</v>
+        <v>5391</v>
       </c>
       <c r="D4" t="n">
-        <v>2926</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>797</v>
+        <v>892</v>
       </c>
       <c r="C5" t="n">
-        <v>2581</v>
+        <v>4476</v>
       </c>
       <c r="D5" t="n">
-        <v>1197</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="C6" t="n">
-        <v>1497</v>
+        <v>1941</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5978</v>
+        <v>1846</v>
       </c>
       <c r="C2" t="n">
-        <v>4944</v>
+        <v>15045</v>
       </c>
       <c r="D2" t="n">
-        <v>19032</v>
+        <v>30078</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3668</v>
+        <v>1626</v>
       </c>
       <c r="C3" t="n">
-        <v>6309</v>
+        <v>7909</v>
       </c>
       <c r="D3" t="n">
-        <v>9395</v>
+        <v>10842</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2097</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="n">
-        <v>5341</v>
+        <v>5578</v>
       </c>
       <c r="D4" t="n">
-        <v>3770</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1071</v>
+        <v>1002</v>
       </c>
       <c r="C5" t="n">
-        <v>3284</v>
+        <v>4830</v>
       </c>
       <c r="D5" t="n">
-        <v>1509</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="C6" t="n">
-        <v>2078</v>
+        <v>3094</v>
       </c>
       <c r="D6" t="n">
-        <v>837</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>1062</v>
+        <v>1150</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4707</v>
+        <v>1740</v>
       </c>
       <c r="C2" t="n">
-        <v>9900</v>
+        <v>9388</v>
       </c>
       <c r="D2" t="n">
-        <v>17637</v>
+        <v>23548</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3937</v>
+        <v>2239</v>
       </c>
       <c r="C3" t="n">
-        <v>4816</v>
+        <v>12114</v>
       </c>
       <c r="D3" t="n">
-        <v>10260</v>
+        <v>12160</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2478</v>
+        <v>925</v>
       </c>
       <c r="C4" t="n">
-        <v>5778</v>
+        <v>8117</v>
       </c>
       <c r="D4" t="n">
-        <v>4735</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1374</v>
+        <v>475</v>
       </c>
       <c r="C5" t="n">
-        <v>4341</v>
+        <v>3032</v>
       </c>
       <c r="D5" t="n">
-        <v>1861</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>712</v>
+        <v>169</v>
       </c>
       <c r="C6" t="n">
-        <v>2670</v>
+        <v>1127</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>628</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>1599</v>
+        <v>359</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>721</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
